--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.67967682467783</v>
+        <v>12.13544748401015</v>
       </c>
       <c r="D2" t="n">
-        <v>74.56916338021466</v>
+        <v>12.11748904928488</v>
       </c>
       <c r="E2" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F2" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.05117633574866</v>
+        <v>9.595816154559158</v>
       </c>
       <c r="D3" t="n">
-        <v>58.94104551173984</v>
+        <v>9.577919895657725</v>
       </c>
       <c r="E3" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F3" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.32534471840535</v>
+        <v>2.81536851674087</v>
       </c>
       <c r="D4" t="n">
-        <v>17.24105689877176</v>
+        <v>2.801671746050411</v>
       </c>
       <c r="E4" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F4" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.80784846002739</v>
+        <v>5.656275374754451</v>
       </c>
       <c r="D5" t="n">
-        <v>34.69608130809875</v>
+        <v>5.638113212566048</v>
       </c>
       <c r="E5" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.8988738044678</v>
+        <v>5.346066993226018</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80377642182459</v>
+        <v>5.330613668546496</v>
       </c>
       <c r="E6" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F6" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.76835542736809</v>
+        <v>2.237357756947315</v>
       </c>
       <c r="D7" t="n">
-        <v>13.73882015859881</v>
+        <v>2.232558275772306</v>
       </c>
       <c r="E7" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F7" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.45615349900305</v>
+        <v>2.511624943587996</v>
       </c>
       <c r="D8" t="n">
-        <v>15.36101353519285</v>
+        <v>2.496164699468838</v>
       </c>
       <c r="E8" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F8" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.8166567996666</v>
+        <v>5.657706729945823</v>
       </c>
       <c r="D9" t="n">
-        <v>34.86977253169314</v>
+        <v>5.666338036400135</v>
       </c>
       <c r="E9" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F9" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.44358321657874</v>
+        <v>6.247082272694046</v>
       </c>
       <c r="D10" t="n">
-        <v>38.5233655644257</v>
+        <v>6.260046904219176</v>
       </c>
       <c r="E10" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F10" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.7968995113872</v>
+        <v>6.14199617060042</v>
       </c>
       <c r="D11" t="n">
-        <v>37.90372719000018</v>
+        <v>6.159355668375029</v>
       </c>
       <c r="E11" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F11" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.78077904956906</v>
+        <v>7.601876595554973</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86347014253379</v>
+        <v>7.615313898161742</v>
       </c>
       <c r="E12" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F12" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.54520561659678</v>
+        <v>6.588595912696977</v>
       </c>
       <c r="D13" t="n">
-        <v>40.64872850209559</v>
+        <v>6.605418381590535</v>
       </c>
       <c r="E13" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F13" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>61.45295645617374</v>
+        <v>9.986105424128233</v>
       </c>
       <c r="D14" t="n">
-        <v>61.55238478180559</v>
+        <v>10.00226252704341</v>
       </c>
       <c r="E14" t="n">
-        <v>17.49042560996551</v>
+        <v>2.842194161619395</v>
       </c>
       <c r="F14" t="n">
-        <v>17.5010314779193</v>
+        <v>2.843917615161887</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
